--- a/fot-app/public/forms/bypass-sheet-itr.xlsx
+++ b/fot-app/public/forms/bypass-sheet-itr.xlsx
@@ -30,7 +30,7 @@
     <t>АХО</t>
   </si>
   <si>
-    <t>Булгаков М.А.</t>
+    <t>Муратов М.Х.</t>
   </si>
   <si>
     <t>ИТ</t>

--- a/fot-app/public/forms/bypass-sheet-itr.xlsx
+++ b/fot-app/public/forms/bypass-sheet-itr.xlsx
@@ -30,7 +30,7 @@
     <t>АХО</t>
   </si>
   <si>
-    <t>Муратов М.Х.</t>
+    <t>Булгаков М.А.</t>
   </si>
   <si>
     <t>ИТ</t>
@@ -102,7 +102,7 @@
     <t>ФИО_________________________________________________________</t>
   </si>
   <si>
-    <t>Белозерова Г.В.</t>
+    <t>Цеунова И.Ю.</t>
   </si>
   <si>
     <t xml:space="preserve">  Дата получения "____" ______________202___ г.</t>
